--- a/Output/AllModels_SensitivityBarriersFacilitators_12000.xlsx
+++ b/Output/AllModels_SensitivityBarriersFacilitators_12000.xlsx
@@ -1,850 +1,857 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kueng\DataAnalysis\02TimeAndTiesControl\Output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80071CD0-0D2C-44C9-9AFF-6651DCC3E4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="2700" yWindow="1185" windowWidth="26910" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Subjective MVPA Hurdle Lognormal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device-Based MVPA Log (Gaussian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mood Gaussian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reactance Dichotome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurdle Component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Zero Component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.)_hu pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI_hu pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.)_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.) pa_obj_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI pa_obj_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. mood_gauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI mood_gauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR is_reactance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI is_reactance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.57,  4.30]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.97***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[42.65, 58.58]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.97***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[109.27, 138.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 3.57,  4.01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.21,    1.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Within-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.23,  1.82]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.97,  1.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.99,   1.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.03,  0.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.49,    0.95]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.12,  1.68]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.98,  1.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.99,   1.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.77,    1.69]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.47,  1.53]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.76,  1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.87,   1.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.19,  0.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.05,   10.65]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.81,  5.29]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.86,  1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.89,   1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.17,  0.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.48,   15.51]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.89,  1.63]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.91,  1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.96,   1.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.03,  0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.07,    2.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.20,  2.51]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.97,   1.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.03,  0.19]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.52,    1.61]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.62,  1.48]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.87,  1.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.89,   1.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.22**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.08,  0.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.37,    3.39]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily barriers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.58,  0.87]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.14,  1.32]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.94,   1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.23***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.29, -0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.44,    1.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily facilitators</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.07,  1.63]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.17,  1.30]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  1.03,   1.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.05,  0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.47,    1.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  1.00,   1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Between-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.24,  2.68]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.75,  1.57]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.76,   1.61]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.56,  0.81]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.37,   48.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.41,  4.31]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.63,  1.30]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.62,   1.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.21,  1.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.50,   88.45]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.04,  1.45]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.25,  1.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.66,   1.90]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.17,  0.61]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.48, 3607.98]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.04,  1.37]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.21,  1.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.56,   1.51]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.17,  0.58]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01,  162.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.20,  7.30]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.76,  3.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.54,   1.76]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.70,  1.43]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02,   85.29]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.22,  7.97]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.83,  3.32]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.72,   2.28]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.15,  0.99]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00,    1.57]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean barriers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.24,  1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.73,  1.19]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.64,   1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.47*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.90, -0.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.08,    5.85]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean facilitators</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.96,  2.79]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.99,  1.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[  0.85,   1.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.03,  0.57]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.20,    2.42]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 3 - Couple)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.75, 1.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.11, 0.37]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.13, 0.38]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.25, 0.71]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.36, 2.86]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.46]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.07, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 0.93]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.52]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.13]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 1.93]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.22]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.29]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.11, 3.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 2.40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.19]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.26]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.13, 4.22]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 0.95]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.15]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.17]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.94]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 1.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.22]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 1.40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.31, 1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.15, 0.34]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.19, 0.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.38, 0.68]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.15, 2.36]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional Parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.62, 0.67]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.50, 0.53]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.79, 0.85]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="275">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Subjective MVPA Hurdle Lognormal</t>
+  </si>
+  <si>
+    <t>Device-Based MVPA Log (Gaussian)</t>
+  </si>
+  <si>
+    <t>Mood Gaussian</t>
+  </si>
+  <si>
+    <t>Reactance Dichotome</t>
+  </si>
+  <si>
+    <t>Hurdle Component</t>
+  </si>
+  <si>
+    <t>Non-Zero Component</t>
+  </si>
+  <si>
+    <t>exp(Est.)_hu pa_sub</t>
+  </si>
+  <si>
+    <t>95% CI_hu pa_sub</t>
+  </si>
+  <si>
+    <t>exp(Est.)_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t>95% CI_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t>exp(Est.) pa_obj_log</t>
+  </si>
+  <si>
+    <t>95% CI pa_obj_log</t>
+  </si>
+  <si>
+    <t>Est. mood_gauss</t>
+  </si>
+  <si>
+    <t>95% CI mood_gauss</t>
+  </si>
+  <si>
+    <t>OR is_reactance</t>
+  </si>
+  <si>
+    <t>95% CI is_reactance</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>2.61***</t>
+  </si>
+  <si>
+    <t>[ 1.57,  4.30]</t>
+  </si>
+  <si>
+    <t>49.97***</t>
+  </si>
+  <si>
+    <t>[42.65, 58.58]</t>
+  </si>
+  <si>
+    <t>122.97***</t>
+  </si>
+  <si>
+    <t>[109.27, 138.25]</t>
+  </si>
+  <si>
+    <t>3.79***</t>
+  </si>
+  <si>
+    <t>[ 3.57,  4.01]</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>[0.21,    1.12]</t>
+  </si>
+  <si>
+    <t>Within-Person Effects</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.47***</t>
+  </si>
+  <si>
+    <t>[ 1.23,  1.82]</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>[ 0.97,  1.09]</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>[  0.99,   1.06]</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>[-0.03,  0.06]</t>
+  </si>
+  <si>
+    <t>0.70*</t>
+  </si>
+  <si>
+    <t>[0.49,    0.95]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.34**</t>
+  </si>
+  <si>
+    <t>[ 1.12,  1.68]</t>
+  </si>
+  <si>
+    <t>[ 0.98,  1.07]</t>
+  </si>
+  <si>
+    <t>[  0.99,   1.07]</t>
+  </si>
+  <si>
+    <t>1.11</t>
+  </si>
+  <si>
+    <t>[0.77,    1.69]</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>[ 0.47,  1.53]</t>
+  </si>
+  <si>
+    <t>0.88*</t>
+  </si>
+  <si>
+    <t>[ 0.76,  1.00]</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>[  0.87,   1.05]</t>
+  </si>
+  <si>
+    <t>-0.06</t>
+  </si>
+  <si>
+    <t>[-0.19,  0.06]</t>
+  </si>
+  <si>
+    <t>2.45*</t>
+  </si>
+  <si>
+    <t>[1.05,   10.65]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced pressure</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
+    <t>[ 0.81,  5.29]</t>
+  </si>
+  <si>
+    <t>[ 0.86,  1.04]</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>[  0.89,   1.03]</t>
+  </si>
+  <si>
+    <t>-0.05</t>
+  </si>
+  <si>
+    <t>[-0.17,  0.06]</t>
+  </si>
+  <si>
+    <t>1.93</t>
+  </si>
+  <si>
+    <t>[0.48,   15.51]</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced pushing</t>
+  </si>
+  <si>
+    <t>1.19</t>
+  </si>
+  <si>
+    <t>[ 0.89,  1.63]</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>[ 0.91,  1.03]</t>
+  </si>
+  <si>
+    <t>[  0.96,   1.08]</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>[-0.03,  0.11]</t>
+  </si>
+  <si>
+    <t>1.45*</t>
+  </si>
+  <si>
+    <t>[1.07,    2.18]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced pushing</t>
+  </si>
+  <si>
+    <t>1.62**</t>
+  </si>
+  <si>
+    <t>[ 1.20,  2.51]</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>[  0.97,   1.06]</t>
+  </si>
+  <si>
+    <t>0.11*</t>
+  </si>
+  <si>
+    <t>[ 0.03,  0.19]</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>[0.52,    1.61]</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>[ 0.62,  1.48]</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>[ 0.87,  1.13]</t>
+  </si>
+  <si>
+    <t>[  0.89,   1.06]</t>
+  </si>
+  <si>
+    <t>0.22**</t>
+  </si>
+  <si>
+    <t>[ 0.08,  0.36]</t>
+  </si>
+  <si>
+    <t>1.13</t>
+  </si>
+  <si>
+    <t>[0.37,    3.39]</t>
+  </si>
+  <si>
+    <t>Own action plan</t>
+  </si>
+  <si>
+    <t>Partner action plan</t>
+  </si>
+  <si>
+    <t>Daily barriers</t>
+  </si>
+  <si>
+    <t>0.71***</t>
+  </si>
+  <si>
+    <t>[ 0.58,  0.87]</t>
+  </si>
+  <si>
+    <t>1.23***</t>
+  </si>
+  <si>
+    <t>[ 1.14,  1.32]</t>
+  </si>
+  <si>
+    <t>[  0.94,   1.03]</t>
+  </si>
+  <si>
+    <t>-0.23***</t>
+  </si>
+  <si>
+    <t>[-0.29, -0.16]</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>[0.44,    1.25]</t>
+  </si>
+  <si>
+    <t>Daily facilitators</t>
+  </si>
+  <si>
+    <t>1.32**</t>
+  </si>
+  <si>
+    <t>[ 1.07,  1.63]</t>
+  </si>
+  <si>
+    <t>1.24***</t>
+  </si>
+  <si>
+    <t>[ 1.17,  1.30]</t>
+  </si>
+  <si>
+    <t>1.07**</t>
+  </si>
+  <si>
+    <t>[  1.03,   1.11]</t>
+  </si>
+  <si>
+    <t>0.11***</t>
+  </si>
+  <si>
+    <t>[ 0.05,  0.16]</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>[0.47,    1.25]</t>
+  </si>
+  <si>
+    <t>Daily wear time</t>
+  </si>
+  <si>
+    <t>1.00***</t>
+  </si>
+  <si>
+    <t>[  1.00,   1.00]</t>
+  </si>
+  <si>
+    <t>Between-Person Effects</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>[ 0.24,  2.68]</t>
+  </si>
+  <si>
+    <t>1.09</t>
+  </si>
+  <si>
+    <t>[ 0.75,  1.57]</t>
+  </si>
+  <si>
+    <t>1.10</t>
+  </si>
+  <si>
+    <t>[  0.76,   1.61]</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>[-0.56,  0.81]</t>
+  </si>
+  <si>
+    <t>3.84</t>
+  </si>
+  <si>
+    <t>[0.37,   48.12]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.34</t>
+  </si>
+  <si>
+    <t>[ 0.41,  4.31]</t>
+  </si>
+  <si>
+    <t>[ 0.63,  1.30]</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>[  0.62,   1.35]</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>[-0.21,  1.16]</t>
+  </si>
+  <si>
+    <t>5.92</t>
+  </si>
+  <si>
+    <t>[0.50,   88.45]</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>[ 0.04,  1.45]</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>[ 0.25,  1.50]</t>
+  </si>
+  <si>
+    <t>[  0.66,   1.90]</t>
+  </si>
+  <si>
+    <t>-0.27</t>
+  </si>
+  <si>
+    <t>[-1.17,  0.61]</t>
+  </si>
+  <si>
+    <t>35.14</t>
+  </si>
+  <si>
+    <t>[0.48, 3607.98]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>[ 0.04,  1.37]</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>[ 0.21,  1.24]</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>[  0.56,   1.51]</t>
+  </si>
+  <si>
+    <t>-0.29</t>
+  </si>
+  <si>
+    <t>[-1.17,  0.58]</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>[0.01,  162.36]</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced pushing</t>
+  </si>
+  <si>
+    <t>[ 0.20,  7.30]</t>
+  </si>
+  <si>
+    <t>[ 0.76,  3.02]</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>[  0.54,   1.76]</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>[-0.70,  1.43]</t>
+  </si>
+  <si>
+    <t>[0.02,   85.29]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced pushing</t>
+  </si>
+  <si>
+    <t>1.32</t>
+  </si>
+  <si>
+    <t>[ 0.22,  7.97]</t>
+  </si>
+  <si>
+    <t>1.66</t>
+  </si>
+  <si>
+    <t>[ 0.83,  3.32]</t>
+  </si>
+  <si>
+    <t>1.27</t>
+  </si>
+  <si>
+    <t>[  0.72,   2.28]</t>
+  </si>
+  <si>
+    <t>[-1.15,  0.99]</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>[0.00,    1.57]</t>
+  </si>
+  <si>
+    <t>Mean barriers</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>[ 0.24,  1.03]</t>
+  </si>
+  <si>
+    <t>[ 0.73,  1.19]</t>
+  </si>
+  <si>
+    <t>[  0.64,   1.03]</t>
+  </si>
+  <si>
+    <t>-0.47*</t>
+  </si>
+  <si>
+    <t>[-0.90, -0.02]</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>[0.08,    5.85]</t>
+  </si>
+  <si>
+    <t>Mean facilitators</t>
+  </si>
+  <si>
+    <t>1.59</t>
+  </si>
+  <si>
+    <t>[ 0.96,  2.79]</t>
+  </si>
+  <si>
+    <t>1.16</t>
+  </si>
+  <si>
+    <t>[ 0.99,  1.36]</t>
+  </si>
+  <si>
+    <t>[  0.85,   1.16]</t>
+  </si>
+  <si>
+    <t>[-0.03,  0.57]</t>
+  </si>
+  <si>
+    <t>[0.20,    2.42]</t>
+  </si>
+  <si>
+    <t>Mean wear time</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>Random Effects (Level 3 - Couple)</t>
+  </si>
+  <si>
+    <t>L3:sd(Intercept)</t>
+  </si>
+  <si>
+    <t>[0.75, 1.60]</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>[0.11, 0.37]</t>
+  </si>
+  <si>
+    <t>[0.13, 0.38]</t>
+  </si>
+  <si>
+    <t>[0.25, 0.71]</t>
+  </si>
+  <si>
+    <t>1.71</t>
+  </si>
+  <si>
+    <t>[0.36, 2.86]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t>0.17</t>
+  </si>
+  <si>
+    <t>[0.01, 0.46]</t>
+  </si>
+  <si>
+    <t>[0.07, 0.18]</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>[0.01, 0.09]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.12]</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>[0.04, 0.93]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>[0.01, 0.52]</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>[0.01, 0.11]</t>
+  </si>
+  <si>
+    <t>[0.01, 0.10]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.13]</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>[0.03, 1.04]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>[0.02, 1.93]</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>[0.00, 0.35]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.22]</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>[0.00, 0.29]</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>[0.11, 3.16]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t>[0.04, 2.40]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.19]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.26]</t>
+  </si>
+  <si>
+    <t>1.64</t>
+  </si>
+  <si>
+    <t>[0.13, 4.22]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t>[0.04, 0.95]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.15]</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>[0.03, 0.17]</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>[0.00, 0.18]</t>
+  </si>
+  <si>
+    <t>[0.02, 0.94]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>[0.03, 1.12]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.11]</t>
+  </si>
+  <si>
+    <t>[0.03, 0.22]</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>[0.03, 1.40]</t>
+  </si>
+  <si>
+    <t>Random Effects (Level 2 - Couple:Person)</t>
+  </si>
+  <si>
+    <t>L2:sd(Intercept)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>[0.31, 1.00]</t>
+  </si>
+  <si>
+    <t>[0.15, 0.34]</t>
+  </si>
+  <si>
+    <t>[0.19, 0.36]</t>
+  </si>
+  <si>
+    <t>[0.38, 0.68]</t>
+  </si>
+  <si>
+    <t>[0.15, 2.36]</t>
+  </si>
+  <si>
+    <t>Additional Parameters</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>[0.62, 0.67]</t>
+  </si>
+  <si>
+    <t>[0.50, 0.53]</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>[0.79, 0.85]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -858,24 +865,30 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <i/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -887,20 +900,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -913,20 +934,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1208,46 +1250,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K45"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="12" width="25.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1282,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1317,7 +1362,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1352,43 +1397,43 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1415,15 +1460,15 @@
       <c r="I6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="12" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1457,8 +1502,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1492,11 +1537,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="11" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1527,8 +1572,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1562,8 +1607,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>78</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1597,8 +1642,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>87</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1632,8 +1677,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>96</v>
       </c>
       <c r="B13" s="1"/>
@@ -1647,8 +1692,8 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>97</v>
       </c>
       <c r="B14" s="1"/>
@@ -1662,8 +1707,8 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>98</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1697,8 +1742,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>108</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -1732,8 +1777,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>119</v>
       </c>
       <c r="B17" s="1"/>
@@ -1751,43 +1796,43 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" s="10" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>123</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1821,8 +1866,8 @@
         <v>133</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>134</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1856,8 +1901,8 @@
         <v>143</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>144</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1891,8 +1936,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1926,8 +1971,8 @@
         <v>164</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>165</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1961,8 +2006,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>173</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1996,8 +2041,8 @@
         <v>182</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>183</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -2031,8 +2076,8 @@
         <v>191</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>192</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2066,8 +2111,8 @@
         <v>199</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>200</v>
       </c>
       <c r="B27" s="1"/>
@@ -2085,43 +2130,43 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="s">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" s="10" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>203</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -2155,8 +2200,8 @@
         <v>210</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>211</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -2190,8 +2235,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>220</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -2225,8 +2270,8 @@
         <v>228</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>229</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -2260,8 +2305,8 @@
         <v>238</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
         <v>239</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -2295,8 +2340,8 @@
         <v>244</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>245</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -2330,8 +2375,8 @@
         <v>252</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
         <v>253</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2365,43 +2410,43 @@
         <v>259</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="J36" s="1" t="s">
+      <c r="J36" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" s="10" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
         <v>261</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -2435,43 +2480,43 @@
         <v>267</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="J38" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" s="10" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="s">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
         <v>269</v>
       </c>
       <c r="B39" s="4"/>
@@ -2497,37 +2542,37 @@
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40">
-      <c r="A40" s="7"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7"/>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="6"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="6"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="6"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A38:K38"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A38:K38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Output/AllModels_SensitivityBarriersFacilitators_12000.xlsx
+++ b/Output/AllModels_SensitivityBarriersFacilitators_12000.xlsx
@@ -1,755 +1,874 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pascku\Repos\02TimeAndTiesControl\Output\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C6EE98-74EB-4A02-8C6B-0A1ABAC640F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="241">
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Subjective MVPA Hurdle Lognormal</t>
-  </si>
-  <si>
-    <t>Device-Based MVPA Log (Gaussian)</t>
-  </si>
-  <si>
-    <t>Mood Gaussian</t>
-  </si>
-  <si>
-    <t>Reactance Dichotome</t>
-  </si>
-  <si>
-    <t>Hurdle Component</t>
-  </si>
-  <si>
-    <t>Non-Zero Component</t>
-  </si>
-  <si>
-    <t>exp(Est.)_hu pa_sub</t>
-  </si>
-  <si>
-    <t>95% CI_hu pa_sub</t>
-  </si>
-  <si>
-    <t>exp(Est.)_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t>95% CI_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t>exp(Est.) pa_obj_log</t>
-  </si>
-  <si>
-    <t>95% CI pa_obj_log</t>
-  </si>
-  <si>
-    <t>Est. mood_gauss</t>
-  </si>
-  <si>
-    <t>95% CI mood_gauss</t>
-  </si>
-  <si>
-    <t>OR is_reactance</t>
-  </si>
-  <si>
-    <t>95% CI is_reactance</t>
-  </si>
-  <si>
-    <t>Intercept</t>
-  </si>
-  <si>
-    <t>2.71***</t>
-  </si>
-  <si>
-    <t>[ 1.62,  4.49]</t>
-  </si>
-  <si>
-    <t>50.57***</t>
-  </si>
-  <si>
-    <t>[42.70, 59.73]</t>
-  </si>
-  <si>
-    <t>123.14***</t>
-  </si>
-  <si>
-    <t>[109.84, 137.96]</t>
-  </si>
-  <si>
-    <t>3.79***</t>
-  </si>
-  <si>
-    <t>[ 3.58,  4.00]</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>[0.23,    1.33]</t>
-  </si>
-  <si>
-    <t>Within-Person Effects</t>
-  </si>
-  <si>
-    <t>Daily individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t>1.58***</t>
-  </si>
-  <si>
-    <t>[ 1.27,  2.10]</t>
-  </si>
-  <si>
-    <t>1.02</t>
-  </si>
-  <si>
-    <t>[ 0.97,  1.07]</t>
-  </si>
-  <si>
-    <t>[  0.98,   1.05]</t>
-  </si>
-  <si>
-    <t>0.01</t>
-  </si>
-  <si>
-    <t>[-0.03,  0.06]</t>
-  </si>
-  <si>
-    <t>0.64**</t>
-  </si>
-  <si>
-    <t>[0.43,    0.88]</t>
-  </si>
-  <si>
-    <t>Daily partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t>1.38***</t>
-  </si>
-  <si>
-    <t>[ 1.14,  1.76]</t>
-  </si>
-  <si>
-    <t>[ 0.98,  1.06]</t>
-  </si>
-  <si>
-    <t>[  0.99,   1.06]</t>
-  </si>
-  <si>
-    <t>[-0.04,  0.05]</t>
-  </si>
-  <si>
-    <t>1.05</t>
-  </si>
-  <si>
-    <t>[0.71,    1.51]</t>
-  </si>
-  <si>
-    <t>Daily individual's experienced pressure</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>[ 0.45,  2.41]</t>
-  </si>
-  <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>[ 0.77,  1.00]</t>
-  </si>
-  <si>
-    <t>0.96</t>
-  </si>
-  <si>
-    <t>[  0.88,   1.06]</t>
-  </si>
-  <si>
-    <t>-0.06</t>
-  </si>
-  <si>
-    <t>[-0.18,  0.06]</t>
-  </si>
-  <si>
-    <t>2.67*</t>
-  </si>
-  <si>
-    <t>[1.19,   16.62]</t>
-  </si>
-  <si>
-    <t>Daily partner's experienced pressure</t>
-  </si>
-  <si>
-    <t>1.87</t>
-  </si>
-  <si>
-    <t>[ 0.90,  9.47]</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>[ 0.86,  1.04]</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>[  0.90,   1.04]</t>
-  </si>
-  <si>
-    <t>-0.04</t>
-  </si>
-  <si>
-    <t>[-0.16,  0.06]</t>
-  </si>
-  <si>
-    <t>1.45</t>
-  </si>
-  <si>
-    <t>[0.35,    7.93]</t>
-  </si>
-  <si>
-    <t>Daily individual's experienced pushing</t>
-  </si>
-  <si>
-    <t>1.21</t>
-  </si>
-  <si>
-    <t>[ 0.90,  1.77]</t>
-  </si>
-  <si>
-    <t>0.98</t>
-  </si>
-  <si>
-    <t>[ 0.92,  1.03]</t>
-  </si>
-  <si>
-    <t>[  0.97,   1.07]</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>[-0.03,  0.11]</t>
-  </si>
-  <si>
-    <t>1.43*</t>
-  </si>
-  <si>
-    <t>[1.05,    2.11]</t>
-  </si>
-  <si>
-    <t>Daily partner's experienced pushing</t>
-  </si>
-  <si>
-    <t>1.68**</t>
-  </si>
-  <si>
-    <t>[ 1.21,  2.89]</t>
-  </si>
-  <si>
-    <t>1.01</t>
-  </si>
-  <si>
-    <t>[  0.97,   1.05]</t>
-  </si>
-  <si>
-    <t>0.11**</t>
-  </si>
-  <si>
-    <t>[ 0.05,  0.18]</t>
-  </si>
-  <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>[0.52,    1.40]</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>[ 0.61,  1.49]</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>[ 0.87,  1.12]</t>
-  </si>
-  <si>
-    <t>0.21**</t>
-  </si>
-  <si>
-    <t>[ 0.07,  0.35]</t>
-  </si>
-  <si>
-    <t>1.06</t>
-  </si>
-  <si>
-    <t>[0.31,    3.38]</t>
-  </si>
-  <si>
-    <t>Own action plan</t>
-  </si>
-  <si>
-    <t>Partner action plan</t>
-  </si>
-  <si>
-    <t>Daily barriers</t>
-  </si>
-  <si>
-    <t>0.70***</t>
-  </si>
-  <si>
-    <t>[ 0.57,  0.86]</t>
-  </si>
-  <si>
-    <t>1.23***</t>
-  </si>
-  <si>
-    <t>[ 1.14,  1.32]</t>
-  </si>
-  <si>
-    <t>[  0.94,   1.03]</t>
-  </si>
-  <si>
-    <t>-0.23***</t>
-  </si>
-  <si>
-    <t>[-0.30, -0.16]</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
-    <t>[0.45,    1.33]</t>
-  </si>
-  <si>
-    <t>Daily facilitators</t>
-  </si>
-  <si>
-    <t>1.31**</t>
-  </si>
-  <si>
-    <t>[ 1.07,  1.63]</t>
-  </si>
-  <si>
-    <t>1.24***</t>
-  </si>
-  <si>
-    <t>[ 1.18,  1.30]</t>
-  </si>
-  <si>
-    <t>1.07***</t>
-  </si>
-  <si>
-    <t>[  1.03,   1.11]</t>
-  </si>
-  <si>
-    <t>0.11***</t>
-  </si>
-  <si>
-    <t>[ 0.05,  0.16]</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>[0.46,    1.26]</t>
-  </si>
-  <si>
-    <t>Daily wear time</t>
-  </si>
-  <si>
-    <t>1.00***</t>
-  </si>
-  <si>
-    <t>[  1.00,   1.00]</t>
-  </si>
-  <si>
-    <t>Between-Person Effects</t>
-  </si>
-  <si>
-    <t>Mean individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>[ 0.25,  2.98]</t>
-  </si>
-  <si>
-    <t>1.10</t>
-  </si>
-  <si>
-    <t>[ 0.74,  1.62]</t>
-  </si>
-  <si>
-    <t>1.09</t>
-  </si>
-  <si>
-    <t>[  0.76,   1.57]</t>
-  </si>
-  <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>[-0.57,  0.78]</t>
-  </si>
-  <si>
-    <t>4.30</t>
-  </si>
-  <si>
-    <t>[0.34,   70.66]</t>
-  </si>
-  <si>
-    <t>Mean partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t>1.42</t>
-  </si>
-  <si>
-    <t>[ 0.41,  4.89]</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>[ 0.61,  1.32]</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>[  0.62,   1.36]</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>[-0.19,  1.16]</t>
-  </si>
-  <si>
-    <t>5.46</t>
-  </si>
-  <si>
-    <t>[0.39,  103.12]</t>
-  </si>
-  <si>
-    <t>Mean individual's experienced pressure</t>
-  </si>
-  <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>[ 0.04,  1.46]</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>[ 0.26,  1.75]</t>
-  </si>
-  <si>
-    <t>[  0.62,   1.80]</t>
-  </si>
-  <si>
-    <t>-0.25</t>
-  </si>
-  <si>
-    <t>[-1.12,  0.61]</t>
-  </si>
-  <si>
-    <t>34.99</t>
-  </si>
-  <si>
-    <t>[0.32, 4935.22]</t>
-  </si>
-  <si>
-    <t>Mean partner's experienced pressure</t>
-  </si>
-  <si>
-    <t>0.18</t>
-  </si>
-  <si>
-    <t>[ 0.03,  1.08]</t>
-  </si>
-  <si>
-    <t>[ 0.19,  1.24]</t>
-  </si>
-  <si>
-    <t>[  0.60,   1.63]</t>
-  </si>
-  <si>
-    <t>-0.28</t>
-  </si>
-  <si>
-    <t>[-1.12,  0.55]</t>
-  </si>
-  <si>
-    <t>2.40</t>
-  </si>
-  <si>
-    <t>[0.01,  425.92]</t>
-  </si>
-  <si>
-    <t>Mean individual's experienced pushing</t>
-  </si>
-  <si>
-    <t>1.13</t>
-  </si>
-  <si>
-    <t>[ 0.17,  7.40]</t>
-  </si>
-  <si>
-    <t>1.38</t>
-  </si>
-  <si>
-    <t>[ 0.66,  2.85]</t>
-  </si>
-  <si>
-    <t>[  0.55,   1.77]</t>
-  </si>
-  <si>
-    <t>0.37</t>
-  </si>
-  <si>
-    <t>[-0.68,  1.42]</t>
-  </si>
-  <si>
-    <t>1.36</t>
-  </si>
-  <si>
-    <t>[0.02,  192.54]</t>
-  </si>
-  <si>
-    <t>Mean partner's experienced pushing</t>
-  </si>
-  <si>
-    <t>1.37</t>
-  </si>
-  <si>
-    <t>[ 0.21,  9.18]</t>
-  </si>
-  <si>
-    <t>1.80</t>
-  </si>
-  <si>
-    <t>[ 0.88,  3.68]</t>
-  </si>
-  <si>
-    <t>1.29</t>
-  </si>
-  <si>
-    <t>[  0.72,   2.34]</t>
-  </si>
-  <si>
-    <t>-0.11</t>
-  </si>
-  <si>
-    <t>[-1.15,  0.93]</t>
-  </si>
-  <si>
-    <t>[0.00,    1.06]</t>
-  </si>
-  <si>
-    <t>Mean barriers</t>
-  </si>
-  <si>
-    <t>[ 0.23,  1.06]</t>
-  </si>
-  <si>
-    <t>[ 0.71,  1.19]</t>
-  </si>
-  <si>
-    <t>0.83</t>
-  </si>
-  <si>
-    <t>[  0.65,   1.08]</t>
-  </si>
-  <si>
-    <t>-0.41</t>
-  </si>
-  <si>
-    <t>[-0.86,  0.06]</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>[0.09,    8.04]</t>
-  </si>
-  <si>
-    <t>Mean facilitators</t>
-  </si>
-  <si>
-    <t>1.67</t>
-  </si>
-  <si>
-    <t>[ 0.96,  3.18]</t>
-  </si>
-  <si>
-    <t>1.12</t>
-  </si>
-  <si>
-    <t>[ 0.95,  1.32]</t>
-  </si>
-  <si>
-    <t>[  0.84,   1.16]</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>[-0.03,  0.57]</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>[0.18,    2.34]</t>
-  </si>
-  <si>
-    <t>Mean wear time</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>Random Effects (Level 3 - Couple)</t>
-  </si>
-  <si>
-    <t>L3:sd(Intercept)</t>
-  </si>
-  <si>
-    <t>1.15</t>
-  </si>
-  <si>
-    <t>[0.73, 1.63]</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>[0.05, 0.39]</t>
-  </si>
-  <si>
-    <t>0.22</t>
-  </si>
-  <si>
-    <t>[0.04, 0.35]</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>[0.15, 0.68]</t>
-  </si>
-  <si>
-    <t>1.65</t>
-  </si>
-  <si>
-    <t>[0.31, 2.77]</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t>L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
-    <t>Random Effects (Level 2 - Couple:Person)</t>
-  </si>
-  <si>
-    <t>L2:sd(Intercept)</t>
-  </si>
-  <si>
-    <t>[0.35, 1.10]</t>
-  </si>
-  <si>
-    <t>[0.16, 0.36]</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>[0.21, 0.40]</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>[0.40, 0.73]</t>
-  </si>
-  <si>
-    <t>1.39</t>
-  </si>
-  <si>
-    <t>[0.19, 2.79]</t>
-  </si>
-  <si>
-    <t>Additional Parameters</t>
-  </si>
-  <si>
-    <t>sigma</t>
-  </si>
-  <si>
-    <t>0.64</t>
-  </si>
-  <si>
-    <t>[0.62, 0.67]</t>
-  </si>
-  <si>
-    <t>0.51</t>
-  </si>
-  <si>
-    <t>[0.49, 0.53]</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>[0.79, 0.85]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="283">
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Subjective MVPA Hurdle Lognormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device-Based MVPA Log (Gaussian)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mood Gaussian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactance Dichotome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurdle Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Zero Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp(Est.)_hu pa_sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI_hu pa_sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp(Est.)_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp(Est.) pa_obj_log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI pa_obj_log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est. mood_gauss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI mood_gauss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OR is_reactance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI is_reactance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.62,  4.49]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.57***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[42.70, 59.73]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.14***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[109.84, 137.96]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 3.58,  4.00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.23,    1.33]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within-Person Effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.27,  2.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.97,  1.07]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.98,   1.05]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.03,  0.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.43,    0.88]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.14,  1.76]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.98,  1.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.99,   1.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.04,  0.05]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.71,    1.51]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily individual's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.45,  2.41]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.77,  1.00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.88,   1.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.18,  0.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1.19,   16.62]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily partner's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.90,  9.47]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.86,  1.04]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.90,   1.04]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.16,  0.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.35,    7.93]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily individual's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.90,  1.77]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.92,  1.03]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.97,   1.07]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.03,  0.11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1.05,    2.11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily partner's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.21,  2.89]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.97,   1.05]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.05,  0.18]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.52,    1.40]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.61,  1.49]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.87,  1.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.07,  0.35]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.31,    3.38]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own action plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner action plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily barriers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.70***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.57,  0.86]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.14,  1.32]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.94,   1.03]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.23***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.30, -0.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.45,    1.33]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily facilitators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.07,  1.63]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 1.18,  1.30]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  1.03,   1.11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.05,  0.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.46,    1.26]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily wear time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  1.00,   1.00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Between-Person Effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.25,  2.98]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.74,  1.62]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.76,   1.57]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.57,  0.78]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.34,   70.66]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.41,  4.89]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.61,  1.32]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.62,   1.36]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.19,  1.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.39,  103.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.04,  1.46]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.26,  1.75]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.62,   1.80]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-1.12,  0.61]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.32, 4935.22]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's experienced pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.03,  1.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.19,  1.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.60,   1.63]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-1.12,  0.55]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01,  425.92]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean individual's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.17,  7.40]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.66,  2.85]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.55,   1.77]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.68,  1.42]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02,  192.54]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean partner's experienced pushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.21,  9.18]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.88,  3.68]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.72,   2.34]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-1.15,  0.93]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00,    1.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean barriers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.23,  1.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.71,  1.19]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.65,   1.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.86,  0.06]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.09,    8.04]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean facilitators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.96,  3.18]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ 0.95,  1.32]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[  0.84,   1.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-0.03,  0.57]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.18,    2.34]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean wear time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random Effects (Level 3 - Couple)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.73, 1.63]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05, 0.39]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 0.35]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.15, 0.68]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.31, 2.77]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.35, 1.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.16, 0.36]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.21, 0.40]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.40, 0.73]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.19, 2.79]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 0.76]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.07, 0.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.15]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.12, 1.15]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.61]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 1.21]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 2.91]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.30]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.20]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.27]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.10, 3.59]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05, 3.02]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.18]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.23]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.09, 4.66]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05, 1.27]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.20]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.95]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 1.62]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.18]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 1.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional Parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sigma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.62, 0.67]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.49, 0.53]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.79, 0.85]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -763,30 +882,24 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <b/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <i/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -798,28 +911,20 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -832,41 +937,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1148,59 +1235,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K45"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.53125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.86328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.3984375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1235,7 +1309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1270,7 +1344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1305,43 +1379,43 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+    <row r="5">
+      <c r="A5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" s="6" t="s">
+    <row r="6">
+      <c r="A6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1368,15 +1442,15 @@
       <c r="I6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="5" t="s">
         <v>37</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" s="6" t="s">
+    <row r="7">
+      <c r="A7" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1410,8 +1484,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" s="6" t="s">
+    <row r="8">
+      <c r="A8" s="7" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1420,7 +1494,7 @@
       <c r="C8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1445,11 +1519,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" s="6" t="s">
+    <row r="9">
+      <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1480,8 +1554,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" s="6" t="s">
+    <row r="10">
+      <c r="A10" s="7" t="s">
         <v>69</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1515,8 +1589,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" s="6" t="s">
+    <row r="11">
+      <c r="A11" s="7" t="s">
         <v>79</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -1550,8 +1624,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" s="6" t="s">
+    <row r="12">
+      <c r="A12" s="7" t="s">
         <v>88</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1585,8 +1659,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" s="6" t="s">
+    <row r="13">
+      <c r="A13" s="7" t="s">
         <v>96</v>
       </c>
       <c r="B13" s="1"/>
@@ -1600,8 +1674,8 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A14" s="6" t="s">
+    <row r="14">
+      <c r="A14" s="7" t="s">
         <v>97</v>
       </c>
       <c r="B14" s="1"/>
@@ -1615,8 +1689,8 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A15" s="6" t="s">
+    <row r="15">
+      <c r="A15" s="7" t="s">
         <v>98</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -1650,8 +1724,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A16" s="6" t="s">
+    <row r="16">
+      <c r="A16" s="7" t="s">
         <v>108</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -1685,8 +1759,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A17" s="6" t="s">
+    <row r="17">
+      <c r="A17" s="7" t="s">
         <v>119</v>
       </c>
       <c r="B17" s="1"/>
@@ -1704,43 +1778,43 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A18" s="9" t="s">
+    <row r="18">
+      <c r="A18" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A19" s="6" t="s">
+    <row r="19">
+      <c r="A19" s="7" t="s">
         <v>123</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1774,8 +1848,8 @@
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A20" s="6" t="s">
+    <row r="20">
+      <c r="A20" s="7" t="s">
         <v>134</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1809,8 +1883,8 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A21" s="6" t="s">
+    <row r="21">
+      <c r="A21" s="7" t="s">
         <v>145</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1844,8 +1918,8 @@
         <v>154</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A22" s="6" t="s">
+    <row r="22">
+      <c r="A22" s="7" t="s">
         <v>155</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1879,8 +1953,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A23" s="6" t="s">
+    <row r="23">
+      <c r="A23" s="7" t="s">
         <v>164</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1914,8 +1988,8 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A24" s="6" t="s">
+    <row r="24">
+      <c r="A24" s="7" t="s">
         <v>174</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1949,8 +2023,8 @@
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A25" s="6" t="s">
+    <row r="25">
+      <c r="A25" s="7" t="s">
         <v>184</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1984,8 +2058,8 @@
         <v>192</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A26" s="6" t="s">
+    <row r="26">
+      <c r="A26" s="7" t="s">
         <v>193</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2019,8 +2093,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A27" s="6" t="s">
+    <row r="27">
+      <c r="A27" s="7" t="s">
         <v>203</v>
       </c>
       <c r="B27" s="1"/>
@@ -2038,43 +2112,43 @@
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A28" s="9" t="s">
+    <row r="28">
+      <c r="A28" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="J28" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="K28" s="10" t="s">
+      <c r="K28" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A29" s="6" t="s">
+    <row r="29">
+      <c r="A29" s="7" t="s">
         <v>206</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -2108,259 +2182,379 @@
         <v>216</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A30" s="6" t="s">
+    <row r="30">
+      <c r="A30" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A31" s="6" t="s">
+      <c r="B30" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A32" s="6" t="s">
+      <c r="B31" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A33" s="6" t="s">
+      <c r="D31" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A34" s="6" t="s">
+      <c r="F31" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A35" s="6" t="s">
+      <c r="G31" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A36" s="9" t="s">
+      <c r="H31" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A37" s="6" t="s">
+      <c r="I31" s="1" t="s">
         <v>224</v>
       </c>
+      <c r="J31" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="s">
+        <v>270</v>
+      </c>
       <c r="B37" s="1" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>146</v>
+        <v>241</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>227</v>
+        <v>75</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>230</v>
+        <v>273</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>231</v>
+        <v>170</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A38" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="K38" s="10" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A39" s="7" t="s">
-        <v>234</v>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="s">
+        <v>276</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A40" s="6"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A41" s="6"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A42" s="6"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A43" s="6"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A44" s="6"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A45" s="6"/>
+    <row r="40">
+      <c r="A40" s="7"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A38:K38"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A38:K38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>